--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -36732,34 +36732,34 @@
       </c>
       <c r="F563" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
-        <v>19312000</v>
+        <v>17670400</v>
       </c>
       <c r="I563" s="5" t="n">
-        <v>31711</v>
+        <v>29015</v>
       </c>
       <c r="J563" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K563" s="5" t="n">
-        <v>17007700</v>
+        <v>17670400</v>
       </c>
       <c r="L563" s="5" t="n">
-        <v>27927</v>
+        <v>29015</v>
       </c>
       <c r="M563" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N563" s="3" t="inlineStr">
@@ -50942,7 +50942,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -50952,7 +50952,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -53102,12 +53102,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1931万
-$31,711/呎
-(在售)</t>
+$1767万
+$29,015/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -16873,7 +16873,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -35166,23 +35166,23 @@
       </c>
       <c r="F538" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
-        <v>13641000</v>
+        <v>12481500</v>
       </c>
       <c r="I538" s="5" t="n">
-        <v>32791</v>
+        <v>30004</v>
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K538" s="5" t="n">
@@ -35193,7 +35193,7 @@
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N538" s="3" t="inlineStr">
@@ -50208,7 +50208,7 @@
           <t>A | 936呎 (3房)
 $3101万
 $33,135/呎
-(26年-08月-14日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -50942,7 +50942,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -50952,7 +50952,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>232</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -52904,12 +52904,12 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 416呎 (1房)
-$1364万
-$32,791/呎
-(在售)</t>
+$1248万
+$30,004/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -17582,38 +17582,30 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H262" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H262" s="5" t="n">
+        <v>30921000</v>
+      </c>
+      <c r="I262" s="5" t="n">
+        <v>33000</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K262" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L262" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K262" s="5" t="n">
+        <v>30921000</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>33000</v>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
@@ -17622,7 +17614,7 @@
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38236,34 +38228,34 @@
       </c>
       <c r="F587" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G587" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H587" s="5" t="n">
-        <v>19076000</v>
+        <v>17454500</v>
       </c>
       <c r="I587" s="5" t="n">
-        <v>31323</v>
+        <v>28661</v>
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
-          <t>11.93%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K587" s="5" t="n">
-        <v>16799900</v>
+        <v>17454500</v>
       </c>
       <c r="L587" s="5" t="n">
-        <v>27586</v>
+        <v>28661</v>
       </c>
       <c r="M587" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減8.5%) + 代繳從價印花稅</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N587" s="3" t="inlineStr">
@@ -48049,7 +48041,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48059,7 +48051,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50298,12 +50290,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 937呎 (3房)
-招标单位
--
-(在售)</t>
+$3092万
+$33,000/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -50942,7 +50934,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -50952,7 +50944,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>233</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -53308,12 +53300,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 609呎 (2房)
-$1908万
-$31,323/呎
-(在售)</t>
+$1745万
+$28,661/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -18296,38 +18296,30 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I273" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="n">
+        <v>30733600</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>32800</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K273" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L273" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K273" s="5" t="n">
+        <v>30733600</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>32800</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
@@ -18336,7 +18328,7 @@
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -48041,7 +48033,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48051,7 +48043,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>198</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50385,12 +50377,12 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 937呎 (3房)
-招标单位
--
-(在售)</t>
+$3073万
+$32,800/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -35146,7 +35146,7 @@
         </is>
       </c>
       <c r="E538" s="4" t="n">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F538" s="3" t="inlineStr">
         <is>
@@ -35155,14 +35155,14 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
         <v>12481500</v>
       </c>
       <c r="I538" s="5" t="n">
-        <v>30004</v>
+        <v>30076</v>
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>12481500</v>
       </c>
       <c r="L538" s="5" t="n">
-        <v>30004</v>
+        <v>30076</v>
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
@@ -52890,10 +52890,10 @@
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>E | 416呎 (1房)
+          <t>E | 415呎 (1房)
 $1248万
-$30,004/呎
-(26年-09月-12日)</t>
+$30,076/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -18292,7 +18292,7 @@
         </is>
       </c>
       <c r="E273" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>30733600</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>32800</v>
+        <v>32835</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>30733600</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>32800</v>
+        <v>32835</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
@@ -50379,9 +50379,9 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3073万
-$32,800/呎
+$32,835/呎
 (26年-09月-22日)</t>
         </is>
       </c>

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -36721,7 +36721,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -53091,7 +53091,7 @@
           <t>D | 609呎 (2房)
 $1767万
 $29,015/呎
-(26年-09月-09日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
@@ -17587,14 +17587,14 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
         <v>30921000</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>33000</v>
+        <v>33035</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>30921000</v>
       </c>
       <c r="L262" s="5" t="n">
-        <v>33000</v>
+        <v>33035</v>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
       </c>
       <c r="G587" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H587" s="5" t="n">
@@ -50284,10 +50284,10 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 937呎 (3房)
+          <t>A | 936呎 (3房)
 $3092万
-$33,000/呎
-(26年-09月-15日)</t>
+$33,035/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -53297,7 +53297,7 @@
           <t>D | 609呎 (2房)
 $1745万
 $28,661/呎
-(26年-09月-15日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -18301,7 +18301,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -50382,7 +50382,7 @@
           <t>A | 936呎 (3房)
 $3073万
 $32,835/呎
-(26年-09月-22日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">

--- a/files/九龙-启德-Henley Park.xlsx
+++ b/files/九龙-启德-Henley Park.xlsx
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>33732000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>36038</v>
+        <v>36000</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>33732000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>36038</v>
+        <v>36000</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>32880000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>35128</v>
+        <v>35091</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>32880000</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>35128</v>
+        <v>35091</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>32795000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>35037</v>
+        <v>35000</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>32795000</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>35037</v>
+        <v>35000</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>32933000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>35185</v>
+        <v>35147</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>32933000</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>35185</v>
+        <v>35147</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>32795000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>35037</v>
+        <v>35000</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>32795000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>35037</v>
+        <v>35000</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>32130000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>34327</v>
+        <v>34290</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>32130000</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>34327</v>
+        <v>34290</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>31951700</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>34136</v>
+        <v>34100</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>31951700</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>34136</v>
+        <v>34100</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>31760000</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>33932</v>
+        <v>33895</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>31760000</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>33932</v>
+        <v>33895</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>31670600</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>33836</v>
+        <v>33800</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>31670600</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>33836</v>
+        <v>33800</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>32045400</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>34237</v>
+        <v>34200</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>32045400</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>34237</v>
+        <v>34200</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>31951700</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>34136</v>
+        <v>34100</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>31951700</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>34136</v>
+        <v>34100</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>31600000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>33761</v>
+        <v>33725</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>31600000</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>33761</v>
+        <v>33725</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>31838000</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>34015</v>
+        <v>33979</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>31838000</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>34015</v>
+        <v>33979</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>31764300</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>33936</v>
+        <v>33900</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>31764300</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>33936</v>
+        <v>33900</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>31670600</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>33836</v>
+        <v>33800</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>31670600</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>33836</v>
+        <v>33800</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>31576900</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>33736</v>
+        <v>33700</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>31576900</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>33736</v>
+        <v>33700</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>30560000</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>32650</v>
+        <v>32615</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>30560000</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>32650</v>
+        <v>32615</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>30513400</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>32600</v>
+        <v>32565</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>30513400</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>32600</v>
+        <v>32565</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         </is>
       </c>
       <c r="E240" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>31110000</v>
       </c>
       <c r="I240" s="5" t="n">
-        <v>33237</v>
+        <v>33202</v>
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>31110000</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>33237</v>
+        <v>33202</v>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="E251" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>31014000</v>
       </c>
       <c r="I251" s="5" t="n">
-        <v>33135</v>
+        <v>33099</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>31014000</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>33135</v>
+        <v>33099</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>30921000</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>33035</v>
+        <v>33000</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>30921000</v>
       </c>
       <c r="L262" s="5" t="n">
-        <v>33035</v>
+        <v>33000</v>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         </is>
       </c>
       <c r="E273" s="4" t="n">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>30733600</v>
       </c>
       <c r="I273" s="5" t="n">
-        <v>32835</v>
+        <v>32800</v>
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>30733600</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>32835</v>
+        <v>32800</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         </is>
       </c>
       <c r="E322" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>8556100</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>21939</v>
+        <v>21995</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>8556100</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>21939</v>
+        <v>21995</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         </is>
       </c>
       <c r="E326" s="4" t="n">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>54225000</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>45037</v>
+        <v>45000</v>
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>54225000</v>
       </c>
       <c r="L326" s="5" t="n">
-        <v>45037</v>
+        <v>45000</v>
       </c>
       <c r="M326" s="3" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         </is>
       </c>
       <c r="E331" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F331" s="3" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>8315100</v>
       </c>
       <c r="I331" s="5" t="n">
-        <v>21321</v>
+        <v>21376</v>
       </c>
       <c r="J331" s="3" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>8315100</v>
       </c>
       <c r="L331" s="5" t="n">
-        <v>21321</v>
+        <v>21376</v>
       </c>
       <c r="M331" s="3" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         </is>
       </c>
       <c r="E343" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>8244000</v>
       </c>
       <c r="I343" s="5" t="n">
-        <v>21138</v>
+        <v>21193</v>
       </c>
       <c r="J343" s="3" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>8244000</v>
       </c>
       <c r="L343" s="5" t="n">
-        <v>21138</v>
+        <v>21193</v>
       </c>
       <c r="M343" s="3" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="E355" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>8384400</v>
       </c>
       <c r="I355" s="5" t="n">
-        <v>21498</v>
+        <v>21554</v>
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>8384400</v>
       </c>
       <c r="L355" s="5" t="n">
-        <v>21498</v>
+        <v>21554</v>
       </c>
       <c r="M355" s="3" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         </is>
       </c>
       <c r="E367" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>8196300</v>
       </c>
       <c r="I367" s="5" t="n">
-        <v>21016</v>
+        <v>21070</v>
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>8196300</v>
       </c>
       <c r="L367" s="5" t="n">
-        <v>21016</v>
+        <v>21070</v>
       </c>
       <c r="M367" s="3" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         </is>
       </c>
       <c r="E373" s="4" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>14557500</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>30712</v>
+        <v>30777</v>
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>14557500</v>
       </c>
       <c r="L373" s="5" t="n">
-        <v>30712</v>
+        <v>30777</v>
       </c>
       <c r="M373" s="3" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         </is>
       </c>
       <c r="E375" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>12884400</v>
       </c>
       <c r="I375" s="5" t="n">
-        <v>21367</v>
+        <v>21332</v>
       </c>
       <c r="J375" s="3" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>12884400</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>21367</v>
+        <v>21332</v>
       </c>
       <c r="M375" s="3" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         </is>
       </c>
       <c r="E379" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>8308200</v>
       </c>
       <c r="I379" s="5" t="n">
-        <v>21303</v>
+        <v>21358</v>
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>8308200</v>
       </c>
       <c r="L379" s="5" t="n">
-        <v>21303</v>
+        <v>21358</v>
       </c>
       <c r="M379" s="3" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         </is>
       </c>
       <c r="E385" s="4" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>14472900</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>30534</v>
+        <v>30598</v>
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>14472900</v>
       </c>
       <c r="L385" s="5" t="n">
-        <v>30534</v>
+        <v>30598</v>
       </c>
       <c r="M385" s="3" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         </is>
       </c>
       <c r="E391" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>8374900</v>
       </c>
       <c r="I391" s="5" t="n">
-        <v>21474</v>
+        <v>21529</v>
       </c>
       <c r="J391" s="3" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>8374900</v>
       </c>
       <c r="L391" s="5" t="n">
-        <v>21474</v>
+        <v>21529</v>
       </c>
       <c r="M391" s="3" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         </is>
       </c>
       <c r="E397" s="4" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>14389200</v>
       </c>
       <c r="I397" s="5" t="n">
-        <v>30357</v>
+        <v>30421</v>
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>14389200</v>
       </c>
       <c r="L397" s="5" t="n">
-        <v>30357</v>
+        <v>30421</v>
       </c>
       <c r="M397" s="3" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         </is>
       </c>
       <c r="E399" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>13197600</v>
       </c>
       <c r="I399" s="5" t="n">
-        <v>21887</v>
+        <v>21850</v>
       </c>
       <c r="J399" s="3" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>13197600</v>
       </c>
       <c r="L399" s="5" t="n">
-        <v>21887</v>
+        <v>21850</v>
       </c>
       <c r="M399" s="3" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         </is>
       </c>
       <c r="E403" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>8190900</v>
       </c>
       <c r="I403" s="5" t="n">
-        <v>21002</v>
+        <v>21056</v>
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>8190900</v>
       </c>
       <c r="L403" s="5" t="n">
-        <v>21002</v>
+        <v>21056</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         </is>
       </c>
       <c r="E415" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>8212100</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>21057</v>
+        <v>21111</v>
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>8212100</v>
       </c>
       <c r="L415" s="5" t="n">
-        <v>21057</v>
+        <v>21111</v>
       </c>
       <c r="M415" s="3" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         </is>
       </c>
       <c r="E427" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>8053200</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>20649</v>
+        <v>20702</v>
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>8053200</v>
       </c>
       <c r="L427" s="5" t="n">
-        <v>20649</v>
+        <v>20702</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>12660300</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>20996</v>
+        <v>20961</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>12660300</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>20996</v>
+        <v>20961</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         </is>
       </c>
       <c r="E439" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>8029800</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>20589</v>
+        <v>20642</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>8029800</v>
       </c>
       <c r="L439" s="5" t="n">
-        <v>20589</v>
+        <v>20642</v>
       </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
@@ -29632,7 +29632,7 @@
         </is>
       </c>
       <c r="E451" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
@@ -29648,7 +29648,7 @@
         <v>8006400</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>20529</v>
+        <v>20582</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>8006400</v>
       </c>
       <c r="L451" s="5" t="n">
-        <v>20529</v>
+        <v>20582</v>
       </c>
       <c r="M451" s="3" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         </is>
       </c>
       <c r="E463" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>7982100</v>
       </c>
       <c r="I463" s="5" t="n">
-        <v>20467</v>
+        <v>20520</v>
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>7982100</v>
       </c>
       <c r="L463" s="5" t="n">
-        <v>20467</v>
+        <v>20520</v>
       </c>
       <c r="M463" s="3" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         </is>
       </c>
       <c r="E475" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>7958700</v>
       </c>
       <c r="I475" s="5" t="n">
-        <v>20407</v>
+        <v>20459</v>
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>7958700</v>
       </c>
       <c r="L475" s="5" t="n">
-        <v>20407</v>
+        <v>20459</v>
       </c>
       <c r="M475" s="3" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         </is>
       </c>
       <c r="E487" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
@@ -31952,7 +31952,7 @@
         <v>7934400</v>
       </c>
       <c r="I487" s="5" t="n">
-        <v>20345</v>
+        <v>20397</v>
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>7934400</v>
       </c>
       <c r="L487" s="5" t="n">
-        <v>20345</v>
+        <v>20397</v>
       </c>
       <c r="M487" s="3" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         </is>
       </c>
       <c r="E495" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
@@ -32472,7 +32472,7 @@
         <v>12510900</v>
       </c>
       <c r="I495" s="5" t="n">
-        <v>20748</v>
+        <v>20713</v>
       </c>
       <c r="J495" s="3" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>12510900</v>
       </c>
       <c r="L495" s="5" t="n">
-        <v>20748</v>
+        <v>20713</v>
       </c>
       <c r="M495" s="3" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         </is>
       </c>
       <c r="E499" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F499" s="3" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>7934400</v>
       </c>
       <c r="I499" s="5" t="n">
-        <v>20345</v>
+        <v>20397</v>
       </c>
       <c r="J499" s="3" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>7934400</v>
       </c>
       <c r="L499" s="5" t="n">
-        <v>20345</v>
+        <v>20397</v>
       </c>
       <c r="M499" s="3" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         </is>
       </c>
       <c r="E511" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F511" s="3" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>8042800</v>
       </c>
       <c r="I511" s="5" t="n">
-        <v>20623</v>
+        <v>20676</v>
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>8042800</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>20623</v>
+        <v>20676</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         </is>
       </c>
       <c r="E523" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F523" s="3" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>7887600</v>
       </c>
       <c r="I523" s="5" t="n">
-        <v>20225</v>
+        <v>20277</v>
       </c>
       <c r="J523" s="3" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>7887600</v>
       </c>
       <c r="L523" s="5" t="n">
-        <v>20225</v>
+        <v>20277</v>
       </c>
       <c r="M523" s="3" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         </is>
       </c>
       <c r="E526" s="4" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F526" s="3" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>12313800</v>
       </c>
       <c r="I526" s="5" t="n">
-        <v>29672</v>
+        <v>29600</v>
       </c>
       <c r="J526" s="3" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>12313800</v>
       </c>
       <c r="L526" s="5" t="n">
-        <v>29672</v>
+        <v>29600</v>
       </c>
       <c r="M526" s="3" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         </is>
       </c>
       <c r="E531" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F531" s="3" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>12398400</v>
       </c>
       <c r="I531" s="5" t="n">
-        <v>20561</v>
+        <v>20527</v>
       </c>
       <c r="J531" s="3" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>12398400</v>
       </c>
       <c r="L531" s="5" t="n">
-        <v>20561</v>
+        <v>20527</v>
       </c>
       <c r="M531" s="3" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         </is>
       </c>
       <c r="E535" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>7863300</v>
       </c>
       <c r="I535" s="5" t="n">
-        <v>20162</v>
+        <v>20214</v>
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>7863300</v>
       </c>
       <c r="L535" s="5" t="n">
-        <v>20162</v>
+        <v>20214</v>
       </c>
       <c r="M535" s="3" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         </is>
       </c>
       <c r="E538" s="4" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F538" s="3" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>12481500</v>
       </c>
       <c r="I538" s="5" t="n">
-        <v>30076</v>
+        <v>30004</v>
       </c>
       <c r="J538" s="3" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>12481500</v>
       </c>
       <c r="L538" s="5" t="n">
-        <v>30076</v>
+        <v>30004</v>
       </c>
       <c r="M538" s="3" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         </is>
       </c>
       <c r="E543" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F543" s="3" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>12704800</v>
       </c>
       <c r="I543" s="5" t="n">
-        <v>21069</v>
+        <v>21034</v>
       </c>
       <c r="J543" s="3" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>12704800</v>
       </c>
       <c r="L543" s="5" t="n">
-        <v>21069</v>
+        <v>21034</v>
       </c>
       <c r="M543" s="3" t="inlineStr">
         <is>
@@ -35712,7 +35712,7 @@
         </is>
       </c>
       <c r="E547" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F547" s="3" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>7839900</v>
       </c>
       <c r="I547" s="5" t="n">
-        <v>20102</v>
+        <v>20154</v>
       </c>
       <c r="J547" s="3" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>7839900</v>
       </c>
       <c r="L547" s="5" t="n">
-        <v>20102</v>
+        <v>20154</v>
       </c>
       <c r="M547" s="3" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         </is>
       </c>
       <c r="E555" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         <v>12323700</v>
       </c>
       <c r="I555" s="5" t="n">
-        <v>20437</v>
+        <v>20403</v>
       </c>
       <c r="J555" s="3" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>12323700</v>
       </c>
       <c r="L555" s="5" t="n">
-        <v>20437</v>
+        <v>20403</v>
       </c>
       <c r="M555" s="3" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         </is>
       </c>
       <c r="E559" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F559" s="3" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>7816500</v>
       </c>
       <c r="I559" s="5" t="n">
-        <v>20042</v>
+        <v>20094</v>
       </c>
       <c r="J559" s="3" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>7816500</v>
       </c>
       <c r="L559" s="5" t="n">
-        <v>20042</v>
+        <v>20094</v>
       </c>
       <c r="M559" s="3" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         </is>
       </c>
       <c r="E567" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F567" s="3" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>12286800</v>
       </c>
       <c r="I567" s="5" t="n">
-        <v>20376</v>
+        <v>20342</v>
       </c>
       <c r="J567" s="3" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>12286800</v>
       </c>
       <c r="L567" s="5" t="n">
-        <v>20376</v>
+        <v>20342</v>
       </c>
       <c r="M567" s="3" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         </is>
       </c>
       <c r="E571" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F571" s="3" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>7947900</v>
       </c>
       <c r="I571" s="5" t="n">
-        <v>20379</v>
+        <v>20432</v>
       </c>
       <c r="J571" s="3" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>7947900</v>
       </c>
       <c r="L571" s="5" t="n">
-        <v>20379</v>
+        <v>20432</v>
       </c>
       <c r="M571" s="3" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         </is>
       </c>
       <c r="E583" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F583" s="3" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>7924500</v>
       </c>
       <c r="I583" s="5" t="n">
-        <v>20319</v>
+        <v>20371</v>
       </c>
       <c r="J583" s="3" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>7924500</v>
       </c>
       <c r="L583" s="5" t="n">
-        <v>20319</v>
+        <v>20371</v>
       </c>
       <c r="M583" s="3" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         </is>
       </c>
       <c r="E591" s="4" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F591" s="3" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>12249000</v>
       </c>
       <c r="I591" s="5" t="n">
-        <v>20313</v>
+        <v>20280</v>
       </c>
       <c r="J591" s="3" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>12249000</v>
       </c>
       <c r="L591" s="5" t="n">
-        <v>20313</v>
+        <v>20280</v>
       </c>
       <c r="M591" s="3" t="inlineStr">
         <is>
@@ -38720,7 +38720,7 @@
         </is>
       </c>
       <c r="E595" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>7924500</v>
       </c>
       <c r="I595" s="5" t="n">
-        <v>20319</v>
+        <v>20371</v>
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>7924500</v>
       </c>
       <c r="L595" s="5" t="n">
-        <v>20319</v>
+        <v>20371</v>
       </c>
       <c r="M595" s="3" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         </is>
       </c>
       <c r="E607" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F607" s="3" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>7830500</v>
       </c>
       <c r="I607" s="5" t="n">
-        <v>20078</v>
+        <v>20130</v>
       </c>
       <c r="J607" s="3" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         <v>7830500</v>
       </c>
       <c r="L607" s="5" t="n">
-        <v>20078</v>
+        <v>20130</v>
       </c>
       <c r="M607" s="3" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         </is>
       </c>
       <c r="E619" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F619" s="3" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>7875900</v>
       </c>
       <c r="I619" s="5" t="n">
-        <v>20195</v>
+        <v>20247</v>
       </c>
       <c r="J619" s="3" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>7875900</v>
       </c>
       <c r="L619" s="5" t="n">
-        <v>20195</v>
+        <v>20247</v>
       </c>
       <c r="M619" s="3" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         </is>
       </c>
       <c r="E631" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F631" s="3" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>7851600</v>
       </c>
       <c r="I631" s="5" t="n">
-        <v>20132</v>
+        <v>20184</v>
       </c>
       <c r="J631" s="3" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>7851600</v>
       </c>
       <c r="L631" s="5" t="n">
-        <v>20132</v>
+        <v>20184</v>
       </c>
       <c r="M631" s="3" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         </is>
       </c>
       <c r="E643" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F643" s="3" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>7803000</v>
       </c>
       <c r="I643" s="5" t="n">
-        <v>20008</v>
+        <v>20059</v>
       </c>
       <c r="J643" s="3" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>7803000</v>
       </c>
       <c r="L643" s="5" t="n">
-        <v>20008</v>
+        <v>20059</v>
       </c>
       <c r="M643" s="3" t="inlineStr">
         <is>
@@ -42496,7 +42496,7 @@
         </is>
       </c>
       <c r="E655" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F655" s="3" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>7730100</v>
       </c>
       <c r="I655" s="5" t="n">
-        <v>19821</v>
+        <v>19872</v>
       </c>
       <c r="J655" s="3" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>7730100</v>
       </c>
       <c r="L655" s="5" t="n">
-        <v>19821</v>
+        <v>19872</v>
       </c>
       <c r="M655" s="3" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         </is>
       </c>
       <c r="E663" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F663" s="3" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>6093000</v>
       </c>
       <c r="I663" s="5" t="n">
-        <v>20043</v>
+        <v>20109</v>
       </c>
       <c r="J663" s="3" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>6093000</v>
       </c>
       <c r="L663" s="5" t="n">
-        <v>20043</v>
+        <v>20109</v>
       </c>
       <c r="M663" s="3" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         </is>
       </c>
       <c r="E664" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F664" s="3" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>6132300</v>
       </c>
       <c r="I664" s="5" t="n">
-        <v>20172</v>
+        <v>20239</v>
       </c>
       <c r="J664" s="3" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>6132300</v>
       </c>
       <c r="L664" s="5" t="n">
-        <v>20172</v>
+        <v>20239</v>
       </c>
       <c r="M664" s="3" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         </is>
       </c>
       <c r="E667" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F667" s="3" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>6157000</v>
       </c>
       <c r="I667" s="5" t="n">
-        <v>20253</v>
+        <v>20320</v>
       </c>
       <c r="J667" s="3" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>6157000</v>
       </c>
       <c r="L667" s="5" t="n">
-        <v>20253</v>
+        <v>20320</v>
       </c>
       <c r="M667" s="3" t="inlineStr">
         <is>
@@ -43326,7 +43326,7 @@
         </is>
       </c>
       <c r="E668" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F668" s="3" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>6096600</v>
       </c>
       <c r="I668" s="5" t="n">
-        <v>20055</v>
+        <v>20121</v>
       </c>
       <c r="J668" s="3" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>6096600</v>
       </c>
       <c r="L668" s="5" t="n">
-        <v>20055</v>
+        <v>20121</v>
       </c>
       <c r="M668" s="3" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         </is>
       </c>
       <c r="E671" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F671" s="3" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>6086000</v>
       </c>
       <c r="I671" s="5" t="n">
-        <v>20020</v>
+        <v>20086</v>
       </c>
       <c r="J671" s="3" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>6086000</v>
       </c>
       <c r="L671" s="5" t="n">
-        <v>20020</v>
+        <v>20086</v>
       </c>
       <c r="M671" s="3" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="E672" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F672" s="3" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>6127200</v>
       </c>
       <c r="I672" s="5" t="n">
-        <v>20155</v>
+        <v>20222</v>
       </c>
       <c r="J672" s="3" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>6127200</v>
       </c>
       <c r="L672" s="5" t="n">
-        <v>20155</v>
+        <v>20222</v>
       </c>
       <c r="M672" s="3" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="E676" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F676" s="3" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>6097600</v>
       </c>
       <c r="I676" s="5" t="n">
-        <v>20058</v>
+        <v>20124</v>
       </c>
       <c r="J676" s="3" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>6097600</v>
       </c>
       <c r="L676" s="5" t="n">
-        <v>20058</v>
+        <v>20124</v>
       </c>
       <c r="M676" s="3" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         </is>
       </c>
       <c r="E682" s="4" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F682" s="3" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>17406400</v>
       </c>
       <c r="I682" s="5" t="n">
-        <v>27806</v>
+        <v>27761</v>
       </c>
       <c r="J682" s="3" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>17406400</v>
       </c>
       <c r="L682" s="5" t="n">
-        <v>27806</v>
+        <v>27761</v>
       </c>
       <c r="M682" s="3" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         </is>
       </c>
       <c r="E694" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F694" s="3" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>14395500</v>
       </c>
       <c r="I694" s="5" t="n">
-        <v>22215</v>
+        <v>22181</v>
       </c>
       <c r="J694" s="3" t="inlineStr">
         <is>
@@ -44965,7 +44965,7 @@
         <v>14395500</v>
       </c>
       <c r="L694" s="5" t="n">
-        <v>22215</v>
+        <v>22181</v>
       </c>
       <c r="M694" s="3" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         </is>
       </c>
       <c r="E695" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F695" s="3" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>6147900</v>
       </c>
       <c r="I695" s="5" t="n">
-        <v>20223</v>
+        <v>20290</v>
       </c>
       <c r="J695" s="3" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>6147900</v>
       </c>
       <c r="L695" s="5" t="n">
-        <v>20223</v>
+        <v>20290</v>
       </c>
       <c r="M695" s="3" t="inlineStr">
         <is>
@@ -45124,7 +45124,7 @@
         </is>
       </c>
       <c r="E697" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F697" s="3" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>14428100</v>
       </c>
       <c r="I697" s="5" t="n">
-        <v>22266</v>
+        <v>22231</v>
       </c>
       <c r="J697" s="3" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>14428100</v>
       </c>
       <c r="L697" s="5" t="n">
-        <v>22266</v>
+        <v>22231</v>
       </c>
       <c r="M697" s="3" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         </is>
       </c>
       <c r="E703" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>6637500</v>
       </c>
       <c r="I703" s="5" t="n">
-        <v>21834</v>
+        <v>21906</v>
       </c>
       <c r="J703" s="3" t="inlineStr">
         <is>
@@ -45523,7 +45523,7 @@
         <v>6637500</v>
       </c>
       <c r="L703" s="5" t="n">
-        <v>21834</v>
+        <v>21906</v>
       </c>
       <c r="M703" s="3" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         </is>
       </c>
       <c r="E705" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F705" s="3" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>14935500</v>
       </c>
       <c r="I705" s="5" t="n">
-        <v>23049</v>
+        <v>23013</v>
       </c>
       <c r="J705" s="3" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>14935500</v>
       </c>
       <c r="L705" s="5" t="n">
-        <v>23049</v>
+        <v>23013</v>
       </c>
       <c r="M705" s="3" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         </is>
       </c>
       <c r="E706" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F706" s="3" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>15207000</v>
       </c>
       <c r="I706" s="5" t="n">
-        <v>23468</v>
+        <v>23431</v>
       </c>
       <c r="J706" s="3" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>15207000</v>
       </c>
       <c r="L706" s="5" t="n">
-        <v>23468</v>
+        <v>23431</v>
       </c>
       <c r="M706" s="3" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         </is>
       </c>
       <c r="E708" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F708" s="3" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>6599300</v>
       </c>
       <c r="I708" s="5" t="n">
-        <v>21708</v>
+        <v>21780</v>
       </c>
       <c r="J708" s="3" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>6599300</v>
       </c>
       <c r="L708" s="5" t="n">
-        <v>21708</v>
+        <v>21780</v>
       </c>
       <c r="M708" s="3" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         </is>
       </c>
       <c r="E710" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F710" s="3" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>14907600</v>
       </c>
       <c r="I710" s="5" t="n">
-        <v>23006</v>
+        <v>22970</v>
       </c>
       <c r="J710" s="3" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>14907600</v>
       </c>
       <c r="L710" s="5" t="n">
-        <v>23006</v>
+        <v>22970</v>
       </c>
       <c r="M710" s="3" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         </is>
       </c>
       <c r="E711" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F711" s="3" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>6741400</v>
       </c>
       <c r="I711" s="5" t="n">
-        <v>22176</v>
+        <v>22249</v>
       </c>
       <c r="J711" s="3" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>6741400</v>
       </c>
       <c r="L711" s="5" t="n">
-        <v>22176</v>
+        <v>22249</v>
       </c>
       <c r="M711" s="3" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         </is>
       </c>
       <c r="E712" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F712" s="3" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>6596200</v>
       </c>
       <c r="I712" s="5" t="n">
-        <v>21698</v>
+        <v>21770</v>
       </c>
       <c r="J712" s="3" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>6596200</v>
       </c>
       <c r="L712" s="5" t="n">
-        <v>21698</v>
+        <v>21770</v>
       </c>
       <c r="M712" s="3" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         </is>
       </c>
       <c r="E715" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F715" s="3" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>6519600</v>
       </c>
       <c r="I715" s="5" t="n">
-        <v>21446</v>
+        <v>21517</v>
       </c>
       <c r="J715" s="3" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>6519600</v>
       </c>
       <c r="L715" s="5" t="n">
-        <v>21446</v>
+        <v>21517</v>
       </c>
       <c r="M715" s="3" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         </is>
       </c>
       <c r="E716" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F716" s="3" t="inlineStr">
         <is>
@@ -46318,7 +46318,7 @@
         <v>6448500</v>
       </c>
       <c r="I716" s="5" t="n">
-        <v>21212</v>
+        <v>21282</v>
       </c>
       <c r="J716" s="3" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>6448500</v>
       </c>
       <c r="L716" s="5" t="n">
-        <v>21212</v>
+        <v>21282</v>
       </c>
       <c r="M716" s="3" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         </is>
       </c>
       <c r="E726" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F726" s="3" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>14006800</v>
       </c>
       <c r="I726" s="5" t="n">
-        <v>21615</v>
+        <v>21582</v>
       </c>
       <c r="J726" s="3" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>14006800</v>
       </c>
       <c r="L726" s="5" t="n">
-        <v>21615</v>
+        <v>21582</v>
       </c>
       <c r="M726" s="3" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         </is>
       </c>
       <c r="E728" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F728" s="3" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>6109200</v>
       </c>
       <c r="I728" s="5" t="n">
-        <v>20096</v>
+        <v>20162</v>
       </c>
       <c r="J728" s="3" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>6109200</v>
       </c>
       <c r="L728" s="5" t="n">
-        <v>20096</v>
+        <v>20162</v>
       </c>
       <c r="M728" s="3" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         </is>
       </c>
       <c r="E730" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F730" s="3" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>13808300</v>
       </c>
       <c r="I730" s="5" t="n">
-        <v>21309</v>
+        <v>21276</v>
       </c>
       <c r="J730" s="3" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>13808300</v>
       </c>
       <c r="L730" s="5" t="n">
-        <v>21309</v>
+        <v>21276</v>
       </c>
       <c r="M730" s="3" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         </is>
       </c>
       <c r="E731" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F731" s="3" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>6108300</v>
       </c>
       <c r="I731" s="5" t="n">
-        <v>20093</v>
+        <v>20159</v>
       </c>
       <c r="J731" s="3" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>6108300</v>
       </c>
       <c r="L731" s="5" t="n">
-        <v>20093</v>
+        <v>20159</v>
       </c>
       <c r="M731" s="3" t="inlineStr">
         <is>
@@ -47294,7 +47294,7 @@
         </is>
       </c>
       <c r="E732" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F732" s="3" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>6173500</v>
       </c>
       <c r="I732" s="5" t="n">
-        <v>20308</v>
+        <v>20375</v>
       </c>
       <c r="J732" s="3" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>6173500</v>
       </c>
       <c r="L732" s="5" t="n">
-        <v>20308</v>
+        <v>20375</v>
       </c>
       <c r="M732" s="3" t="inlineStr">
         <is>
@@ -47418,7 +47418,7 @@
         </is>
       </c>
       <c r="E734" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F734" s="3" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>13801800</v>
       </c>
       <c r="I734" s="5" t="n">
-        <v>21299</v>
+        <v>21266</v>
       </c>
       <c r="J734" s="3" t="inlineStr">
         <is>
@@ -47445,7 +47445,7 @@
         <v>13801800</v>
       </c>
       <c r="L734" s="5" t="n">
-        <v>21299</v>
+        <v>21266</v>
       </c>
       <c r="M734" s="3" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         </is>
       </c>
       <c r="E735" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F735" s="3" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>6071400</v>
       </c>
       <c r="I735" s="5" t="n">
-        <v>19972</v>
+        <v>20038</v>
       </c>
       <c r="J735" s="3" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>6071400</v>
       </c>
       <c r="L735" s="5" t="n">
-        <v>19972</v>
+        <v>20038</v>
       </c>
       <c r="M735" s="3" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         </is>
       </c>
       <c r="E736" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F736" s="3" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>6102400</v>
       </c>
       <c r="I736" s="5" t="n">
-        <v>20074</v>
+        <v>20140</v>
       </c>
       <c r="J736" s="3" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>6102400</v>
       </c>
       <c r="L736" s="5" t="n">
-        <v>20074</v>
+        <v>20140</v>
       </c>
       <c r="M736" s="3" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         </is>
       </c>
       <c r="E737" s="4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F737" s="3" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>13591800</v>
       </c>
       <c r="I737" s="5" t="n">
-        <v>20975</v>
+        <v>20943</v>
       </c>
       <c r="J737" s="3" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>13591800</v>
       </c>
       <c r="L737" s="5" t="n">
-        <v>20975</v>
+        <v>20943</v>
       </c>
       <c r="M737" s="3" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         </is>
       </c>
       <c r="E741" s="4" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F741" s="3" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>16854300</v>
       </c>
       <c r="I741" s="5" t="n">
-        <v>26924</v>
+        <v>26881</v>
       </c>
       <c r="J741" s="3" t="inlineStr">
         <is>
@@ -47879,7 +47879,7 @@
         <v>16854300</v>
       </c>
       <c r="L741" s="5" t="n">
-        <v>26924</v>
+        <v>26881</v>
       </c>
       <c r="M741" s="3" t="inlineStr">
         <is>
@@ -48384,9 +48384,9 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3373万
-$36,038/呎
+$36,000/呎
 (26年-06月-23日)</t>
         </is>
       </c>
@@ -48479,9 +48479,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3288万
-$35,128/呎
+$35,091/呎
 (26年-06月-09日)</t>
         </is>
       </c>
@@ -48574,9 +48574,9 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3280万
-$35,037/呎
+$35,000/呎
 (24年-05月-29日)</t>
         </is>
       </c>
@@ -48669,9 +48669,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3293万
-$35,185/呎
+$35,147/呎
 (24年-05月-31日)</t>
         </is>
       </c>
@@ -48764,9 +48764,9 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3280万
-$35,037/呎
+$35,000/呎
 (26年-07月-03日)</t>
         </is>
       </c>
@@ -48859,9 +48859,9 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3213万
-$34,327/呎
+$34,290/呎
 (24年-05月-09日)</t>
         </is>
       </c>
@@ -48954,9 +48954,9 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3195万
-$34,136/呎
+$34,100/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -49049,9 +49049,9 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3176万
-$33,932/呎
+$33,895/呎
 (26年-02月-24日)</t>
         </is>
       </c>
@@ -49144,9 +49144,9 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3167万
-$33,836/呎
+$33,800/呎
 (26年-04月-22日)</t>
         </is>
       </c>
@@ -49239,9 +49239,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3205万
-$34,237/呎
+$34,200/呎
 (26年-06月-23日)</t>
         </is>
       </c>
@@ -49334,9 +49334,9 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3195万
-$34,136/呎
+$34,100/呎
 (26年-07月-22日)</t>
         </is>
       </c>
@@ -49429,9 +49429,9 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3160万
-$33,761/呎
+$33,725/呎
 (26年-07月-09日)</t>
         </is>
       </c>
@@ -49524,9 +49524,9 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3184万
-$34,015/呎
+$33,979/呎
 (26年-08月-05日)</t>
         </is>
       </c>
@@ -49619,9 +49619,9 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3176万
-$33,936/呎
+$33,900/呎
 (26年-07月-16日)</t>
         </is>
       </c>
@@ -49714,9 +49714,9 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3167万
-$33,836/呎
+$33,800/呎
 (26年-07月-16日)</t>
         </is>
       </c>
@@ -49809,9 +49809,9 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3158万
-$33,736/呎
+$33,700/呎
 (26年-07月-16日)</t>
         </is>
       </c>
@@ -49904,9 +49904,9 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3056万
-$32,650/呎
+$32,615/呎
 (26年-08月-20日)</t>
         </is>
       </c>
@@ -49999,9 +49999,9 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3051万
-$32,600/呎
+$32,565/呎
 (26年-08月-20日)</t>
         </is>
       </c>
@@ -50094,9 +50094,9 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3111万
-$33,237/呎
+$33,202/呎
 (26年-08月-25日)</t>
         </is>
       </c>
@@ -50189,9 +50189,9 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3101万
-$33,135/呎
+$33,099/呎
 (26年-09月-11日)</t>
         </is>
       </c>
@@ -50284,9 +50284,9 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3092万
-$33,035/呎
+$33,000/呎
 (26年-10月-14日)</t>
         </is>
       </c>
@@ -50379,9 +50379,9 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>A | 936呎 (3房)
+          <t>A | 937呎 (3房)
 $3073万
-$32,835/呎
+$32,800/呎
 (26年-10月-20日)</t>
         </is>
       </c>
@@ -51025,9 +51025,9 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1204呎 (3房)
+          <t>A | 1205呎 (3房)
 $5422万
-$45,037/呎
+$45,000/呎
 (24年-05月-28日)</t>
         </is>
       </c>
@@ -51057,9 +51057,9 @@
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>E | 390呎 (1房)
+          <t>E | 389呎 (1房)
 $856万
-$21,939/呎
+$21,995/呎
 (25年-07月-31日)</t>
         </is>
       </c>
@@ -51163,9 +51163,9 @@
       </c>
       <c r="I6" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $832万
-$21,321/呎
+$21,376/呎
 (24年-04月-19日)</t>
         </is>
       </c>
@@ -51266,9 +51266,9 @@
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $824万
-$21,138/呎
+$21,193/呎
 (24年-05月-02日)</t>
         </is>
       </c>
@@ -51369,9 +51369,9 @@
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $838万
-$21,498/呎
+$21,554/呎
 (24年-04月-30日)</t>
         </is>
       </c>
@@ -51424,9 +51424,9 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 474呎 (1房)
+          <t>B | 473呎 (1房)
 $1456万
-$30,712/呎
+$30,777/呎
 (26年-05月-12日)</t>
         </is>
       </c>
@@ -51472,9 +51472,9 @@
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $820万
-$21,016/呎
+$21,070/呎
 (24年-04月-17日)</t>
         </is>
       </c>
@@ -51527,9 +51527,9 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>B | 474呎 (1房)
+          <t>B | 473呎 (1房)
 $1447万
-$30,534/呎
+$30,598/呎
 (26年-06月-03日)</t>
         </is>
       </c>
@@ -51575,9 +51575,9 @@
       </c>
       <c r="I10" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $831万
-$21,303/呎
+$21,358/呎
 (24年-04月-19日)</t>
         </is>
       </c>
@@ -51607,9 +51607,9 @@
       </c>
       <c r="M10" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1288万
-$21,367/呎
+$21,332/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -51630,9 +51630,9 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 474呎 (1房)
+          <t>B | 473呎 (1房)
 $1439万
-$30,357/呎
+$30,421/呎
 (26年-04月-15日)</t>
         </is>
       </c>
@@ -51678,9 +51678,9 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $837万
-$21,474/呎
+$21,529/呎
 (24年-04月-16日)</t>
         </is>
       </c>
@@ -51781,9 +51781,9 @@
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $819万
-$21,002/呎
+$21,056/呎
 (24年-04月-11日)</t>
         </is>
       </c>
@@ -51813,9 +51813,9 @@
       </c>
       <c r="M12" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1320万
-$21,887/呎
+$21,850/呎
 (23年-08月-08日)</t>
         </is>
       </c>
@@ -51884,9 +51884,9 @@
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $821万
-$21,057/呎
+$21,111/呎
 (23年-11月-21日)</t>
         </is>
       </c>
@@ -51987,9 +51987,9 @@
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $805万
-$20,649/呎
+$20,702/呎
 (23年-12月-29日)</t>
         </is>
       </c>
@@ -52090,9 +52090,9 @@
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $803万
-$20,589/呎
+$20,642/呎
 (24年-04月-12日)</t>
         </is>
       </c>
@@ -52122,9 +52122,9 @@
       </c>
       <c r="M15" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1266万
-$20,996/呎
+$20,961/呎
 (23年-07月-28日)</t>
         </is>
       </c>
@@ -52193,9 +52193,9 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $801万
-$20,529/呎
+$20,582/呎
 (23年-12月-05日)</t>
         </is>
       </c>
@@ -52296,9 +52296,9 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $798万
-$20,467/呎
+$20,520/呎
 (24年-04月-05日)</t>
         </is>
       </c>
@@ -52399,9 +52399,9 @@
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $796万
-$20,407/呎
+$20,459/呎
 (23年-11月-17日)</t>
         </is>
       </c>
@@ -52502,9 +52502,9 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $793万
-$20,345/呎
+$20,397/呎
 (24年-03月-22日)</t>
         </is>
       </c>
@@ -52605,9 +52605,9 @@
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $793万
-$20,345/呎
+$20,397/呎
 (24年-03月-22日)</t>
         </is>
       </c>
@@ -52637,9 +52637,9 @@
       </c>
       <c r="M20" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1251万
-$20,748/呎
+$20,713/呎
 (23年-08月-08日)</t>
         </is>
       </c>
@@ -52708,9 +52708,9 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $804万
-$20,623/呎
+$20,676/呎
 (24年-04月-08日)</t>
         </is>
       </c>
@@ -52787,9 +52787,9 @@
       </c>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t>E | 415呎 (1房)
+          <t>E | 416呎 (1房)
 $1231万
-$29,672/呎
+$29,600/呎
 (26年-04月-24日)</t>
         </is>
       </c>
@@ -52811,9 +52811,9 @@
       </c>
       <c r="I22" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $789万
-$20,225/呎
+$20,277/呎
 (24年-04月-03日)</t>
         </is>
       </c>
@@ -52890,9 +52890,9 @@
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>E | 415呎 (1房)
+          <t>E | 416呎 (1房)
 $1248万
-$30,076/呎
+$30,004/呎
 (26年-09月-28日)</t>
         </is>
       </c>
@@ -52914,9 +52914,9 @@
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $786万
-$20,162/呎
+$20,214/呎
 (24年-05月-02日)</t>
         </is>
       </c>
@@ -52946,9 +52946,9 @@
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1240万
-$20,561/呎
+$20,527/呎
 (23年-08月-04日)</t>
         </is>
       </c>
@@ -53017,9 +53017,9 @@
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $784万
-$20,102/呎
+$20,154/呎
 (24年-05月-03日)</t>
         </is>
       </c>
@@ -53049,9 +53049,9 @@
       </c>
       <c r="M24" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1270万
-$21,069/呎
+$21,034/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -53120,9 +53120,9 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $782万
-$20,042/呎
+$20,094/呎
 (24年-05月-02日)</t>
         </is>
       </c>
@@ -53152,9 +53152,9 @@
       </c>
       <c r="M25" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1232万
-$20,437/呎
+$20,403/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -53223,9 +53223,9 @@
       </c>
       <c r="I26" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $795万
-$20,379/呎
+$20,432/呎
 (24年-05月-03日)</t>
         </is>
       </c>
@@ -53255,9 +53255,9 @@
       </c>
       <c r="M26" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1229万
-$20,376/呎
+$20,342/呎
 (23年-08月-02日)</t>
         </is>
       </c>
@@ -53326,9 +53326,9 @@
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $792万
-$20,319/呎
+$20,371/呎
 (24年-05月-02日)</t>
         </is>
       </c>
@@ -53429,9 +53429,9 @@
       </c>
       <c r="I28" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $792万
-$20,319/呎
+$20,371/呎
 (24年-05月-03日)</t>
         </is>
       </c>
@@ -53461,9 +53461,9 @@
       </c>
       <c r="M28" s="21" t="inlineStr">
         <is>
-          <t>M | 603呎 (2房)
+          <t>M | 604呎 (2房)
 $1225万
-$20,313/呎
+$20,280/呎
 (23年-08月-01日)</t>
         </is>
       </c>
@@ -53532,9 +53532,9 @@
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $783万
-$20,078/呎
+$20,130/呎
 (24年-05月-03日)</t>
         </is>
       </c>
@@ -53635,9 +53635,9 @@
       </c>
       <c r="I30" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $788万
-$20,195/呎
+$20,247/呎
 (24年-04月-30日)</t>
         </is>
       </c>
@@ -53738,9 +53738,9 @@
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $785万
-$20,132/呎
+$20,184/呎
 (24年-05月-17日)</t>
         </is>
       </c>
@@ -53841,9 +53841,9 @@
       </c>
       <c r="I32" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $780万
-$20,008/呎
+$20,059/呎
 (24年-05月-23日)</t>
         </is>
       </c>
@@ -53944,9 +53944,9 @@
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
-          <t>H | 390呎 (1房)
+          <t>H | 389呎 (1房)
 $773万
-$19,821/呎
+$19,872/呎
 (24年-06月-11日)</t>
         </is>
       </c>
@@ -54130,17 +54130,17 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $613万
-$20,172/呎
+$20,239/呎
 (23年-07月-24日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $609万
-$20,043/呎
+$20,109/呎
 (23年-07月-25日)</t>
         </is>
       </c>
@@ -54169,17 +54169,17 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $610万
-$20,055/呎
+$20,121/呎
 (23年-07月-31日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $616万
-$20,253/呎
+$20,320/呎
 (23年-07月-24日)</t>
         </is>
       </c>
@@ -54208,17 +54208,17 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $613万
-$20,155/呎
+$20,222/呎
 (23年-07月-26日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $609万
-$20,020/呎
+$20,086/呎
 (23年-07月-26日)</t>
         </is>
       </c>
@@ -54247,9 +54247,9 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $610万
-$20,058/呎
+$20,124/呎
 (23年-07月-26日)</t>
         </is>
       </c>
@@ -54270,9 +54270,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 626呎 (3房)
+          <t>A | 627呎 (3房)
 $1741万
-$27,806/呎
+$27,761/呎
 (23年-07月-27日)</t>
         </is>
       </c>
@@ -54510,9 +54510,9 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 648呎 (3房)
+          <t>A | 649呎 (3房)
 $1440万
-$22,215/呎
+$22,181/呎
 (23年-07月-19日)</t>
         </is>
       </c>
@@ -54557,9 +54557,9 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 648呎 (3房)
+          <t>B | 649呎 (3房)
 $1443万
-$22,266/呎
+$22,231/呎
 (23年-07月-24日)</t>
         </is>
       </c>
@@ -54573,9 +54573,9 @@
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $615万
-$20,223/呎
+$20,290/呎
 (23年-07月-21日)</t>
         </is>
       </c>
@@ -54750,17 +54750,17 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 648呎 (3房)
+          <t>A | 649呎 (3房)
 $1521万
-$23,468/呎
+$23,431/呎
 (23年-07月-31日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 648呎 (3房)
+          <t>B | 649呎 (3房)
 $1494万
-$23,049/呎
+$23,013/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -54774,9 +54774,9 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $664万
-$21,834/呎
+$21,906/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -54789,9 +54789,9 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 648呎 (3房)
+          <t>A | 649呎 (3房)
 $1491万
-$23,006/呎
+$22,970/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -54805,9 +54805,9 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $660万
-$21,708/呎
+$21,780/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -54844,17 +54844,17 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $660万
-$21,698/呎
+$21,770/呎
 (23年-08月-03日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $674万
-$22,176/呎
+$22,249/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -54883,17 +54883,17 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $645万
-$21,212/呎
+$21,282/呎
 (23年-08月-07日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $652万
-$21,446/呎
+$21,517/呎
 (23年-07月-11日)</t>
         </is>
       </c>
@@ -55068,9 +55068,9 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 648呎 (3房)
+          <t>A | 649呎 (3房)
 $1401万
-$21,615/呎
+$21,582/呎
 (23年-07月-20日)</t>
         </is>
       </c>
@@ -55107,9 +55107,9 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 648呎 (3房)
+          <t>A | 649呎 (3房)
 $1381万
-$21,309/呎
+$21,276/呎
 (23年-07月-28日)</t>
         </is>
       </c>
@@ -55123,9 +55123,9 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $611万
-$20,096/呎
+$20,162/呎
 (23年-07月-19日)</t>
         </is>
       </c>
@@ -55146,9 +55146,9 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 648呎 (3房)
+          <t>A | 649呎 (3房)
 $1380万
-$21,299/呎
+$21,266/呎
 (23年-07月-20日)</t>
         </is>
       </c>
@@ -55162,17 +55162,17 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $617万
-$20,308/呎
+$20,375/呎
 (23年-07月-19日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $611万
-$20,093/呎
+$20,159/呎
 (23年-07月-26日)</t>
         </is>
       </c>
@@ -55193,25 +55193,25 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 648呎 (3房)
+          <t>B | 649呎 (3房)
 $1359万
-$20,975/呎
+$20,943/呎
 (23年-07月-25日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>C | 304呎 (1房)
+          <t>C | 303呎 (1房)
 $610万
-$20,074/呎
+$20,140/呎
 (23年-07月-19日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>D | 304呎 (1房)
+          <t>D | 303呎 (1房)
 $607万
-$19,972/呎
+$20,038/呎
 (23年-07月-21日)</t>
         </is>
       </c>
@@ -55232,9 +55232,9 @@
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 626呎 (3房)
+          <t>B | 627呎 (3房)
 $1685万
-$26,924/呎
+$26,881/呎
 (23年-07月-20日)</t>
         </is>
       </c>
